--- a/naver-place-crawler/results_hair/성동_미용실.xlsx
+++ b/naver-place-crawler/results_hair/성동_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V586"/>
+  <dimension ref="A1:V609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -49133,34 +49133,30 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>오땡큐 금호4가동점</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>jys6622@naver.com</t>
-        </is>
-      </c>
+          <t>텍스처 서울숲점</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t>02-2282-1784</t>
+          <t>0507-1478-0775</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 동호로2길 27-1</t>
+          <t>서울특별시 성동구 아차산로 6 1동 2층</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/texture_officiale</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -49170,7 +49166,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -49191,17 +49187,17 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P527" t="n">
-        <v>41</v>
+        <v>1517</v>
       </c>
       <c r="Q527" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R527" t="n">
-        <v>41</v>
+        <v>1767</v>
       </c>
       <c r="S527" t="inlineStr">
         <is>
@@ -49210,12 +49206,12 @@
       </c>
       <c r="T527" t="inlineStr">
         <is>
-          <t>1531156447</t>
+          <t>1554787693</t>
         </is>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531156447</t>
+          <t>https://m.place.naver.com/place/1554787693</t>
         </is>
       </c>
       <c r="V527" t="inlineStr">
@@ -49227,29 +49223,29 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>안나스파염색</t>
+          <t>마고미용실</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>saionsss@naver.com</t>
+          <t>kas0220@naver.com</t>
         </is>
       </c>
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
-          <t>0507-1345-1513</t>
+          <t>02-515-6612</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학봉길 42 1층</t>
+          <t>서울특별시 성동구 금호로 40 상가동 지1층 25호</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -49289,13 +49285,13 @@
         </is>
       </c>
       <c r="P528" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q528" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R528" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="S528" t="inlineStr">
         <is>
@@ -49304,12 +49300,12 @@
       </c>
       <c r="T528" t="inlineStr">
         <is>
-          <t>1840237329</t>
+          <t>1236139498</t>
         </is>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840237329</t>
+          <t>https://m.place.naver.com/place/1236139498</t>
         </is>
       </c>
       <c r="V528" t="inlineStr">
@@ -49321,49 +49317,49 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>컬러드스파 왕십리센트라스점</t>
+          <t>더레이디 서울본점</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>7seven_avenue@naver.com</t>
+          <t>steomark@naver.com</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
-          <t>0507-1347-6743</t>
+          <t>0507-1411-8901</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로 410 센트라스 상가 i동 139호 컬러드스파 왕십리센트라스점</t>
+          <t>서울특별시 성동구 왕십리로26길 10-1 1층 더레이디</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>https://colordespa.com/</t>
+          <t>https://www.instagram.com/thelady_seoul?igsh=MWtsZnY5aHVodGtlMw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -49374,7 +49370,7 @@
       <c r="M529" t="inlineStr"/>
       <c r="N529" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
@@ -49383,13 +49379,13 @@
         </is>
       </c>
       <c r="P529" t="n">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="Q529" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="R529" t="n">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="S529" t="inlineStr">
         <is>
@@ -49398,12 +49394,12 @@
       </c>
       <c r="T529" t="inlineStr">
         <is>
-          <t>2011248177</t>
+          <t>31777860</t>
         </is>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011248177</t>
+          <t>https://m.place.naver.com/place/31777860</t>
         </is>
       </c>
       <c r="V529" t="inlineStr">
@@ -49415,34 +49411,34 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>머리염색</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>구피샵 금호점</t>
+          <t>온감헤어</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>jiaesk97@naver.com</t>
+          <t>ongamhair@naver.com</t>
         </is>
       </c>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
-          <t>02-2234-6001</t>
+          <t>0507-1468-0495</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 장터5길 3-1 구피샵</t>
+          <t>서울특별시 성동구 마조로 14 2층, 온감헤어</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ongam_hair</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -49452,7 +49448,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -49473,17 +49469,17 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P530" t="n">
-        <v>74</v>
+        <v>725</v>
       </c>
       <c r="Q530" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R530" t="n">
-        <v>75</v>
+        <v>747</v>
       </c>
       <c r="S530" t="inlineStr">
         <is>
@@ -49492,12 +49488,12 @@
       </c>
       <c r="T530" t="inlineStr">
         <is>
-          <t>1526743661</t>
+          <t>1307195810</t>
         </is>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1526743661</t>
+          <t>https://m.place.naver.com/place/1307195810</t>
         </is>
       </c>
       <c r="V530" t="inlineStr">
@@ -49509,30 +49505,34 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>미용기기,재료</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>한진미용재료</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr"/>
+          <t>프라우디 헤어 왕십리점</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2219480@naver.com</t>
+        </is>
+      </c>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
-          <t>0507-1338-9467</t>
+          <t>0507-1446-3428</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로 322 1층 한진미용상사</t>
+          <t>서울특별시 성동구 무학봉28길 22 2층</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/prou.d_official</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -49542,7 +49542,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -49563,17 +49563,17 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P531" t="n">
-        <v>275</v>
+        <v>1092</v>
       </c>
       <c r="Q531" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R531" t="n">
-        <v>276</v>
+        <v>1130</v>
       </c>
       <c r="S531" t="inlineStr">
         <is>
@@ -49582,12 +49582,12 @@
       </c>
       <c r="T531" t="inlineStr">
         <is>
-          <t>11561901</t>
+          <t>1573399696</t>
         </is>
       </c>
       <c r="U531" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11561901</t>
+          <t>https://m.place.naver.com/place/1573399696</t>
         </is>
       </c>
       <c r="V531" t="inlineStr">
@@ -49599,34 +49599,30 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>텐즈힐애견미용</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>ksj940412@naver.com</t>
-        </is>
-      </c>
+          <t>웨어하우스 성수점</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>0507-1321-7924</t>
+          <t>0507-1358-6917</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 마장로 137 텐즈힐 상가 1층 213동 114호</t>
+          <t>서울특별시 성동구 서울숲2길 24-7 2층, 3층</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/ksj940412</t>
+          <t>https://www.instagram.com/wearhouse_family</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -49641,7 +49637,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -49661,13 +49657,13 @@
         </is>
       </c>
       <c r="P532" t="n">
-        <v>19</v>
+        <v>1264</v>
       </c>
       <c r="Q532" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R532" t="n">
-        <v>115</v>
+        <v>1362</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -49676,12 +49672,12 @@
       </c>
       <c r="T532" t="inlineStr">
         <is>
-          <t>1822735132</t>
+          <t>1885908864</t>
         </is>
       </c>
       <c r="U532" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1822735132</t>
+          <t>https://m.place.naver.com/place/1885908864</t>
         </is>
       </c>
       <c r="V532" t="inlineStr">
@@ -49693,17 +49689,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>베이글버트그루밍</t>
+          <t>정들러미용실</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>mnene@naver.com</t>
+          <t>ksy8557@naver.com</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
@@ -49711,12 +49707,12 @@
       <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로4가길 2-9</t>
+          <t>서울특별시 성동구 독서당로51길 15</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mnene</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -49726,12 +49722,12 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -49747,17 +49743,17 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P533" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q533" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R533" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -49766,12 +49762,12 @@
       </c>
       <c r="T533" t="inlineStr">
         <is>
-          <t>1423888123</t>
+          <t>1369453522</t>
         </is>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423888123</t>
+          <t>https://m.place.naver.com/place/1369453522</t>
         </is>
       </c>
       <c r="V533" t="inlineStr">
@@ -49783,34 +49779,34 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>솜소밍</t>
+          <t>누브아 옥수점</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>somsoming__@naver.com</t>
+          <t>nousvoir2@naver.com</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
-          <t>0507-1367-7210</t>
+          <t>0507-1404-3428</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 고산자로14길 26 지웰홈스 왕십리 상가 1층 솜소밍</t>
+          <t>서울특별시 성동구 한림말3길 20 1층</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/somsoming__</t>
+          <t>https://blog.naver.com/nousvoir2</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -49841,17 +49837,17 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P534" t="n">
-        <v>74</v>
+        <v>1804</v>
       </c>
       <c r="Q534" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="R534" t="n">
-        <v>87</v>
+        <v>1844</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -49860,12 +49856,12 @@
       </c>
       <c r="T534" t="inlineStr">
         <is>
-          <t>1571638964</t>
+          <t>1099191099</t>
         </is>
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571638964</t>
+          <t>https://m.place.naver.com/place/1099191099</t>
         </is>
       </c>
       <c r="V534" t="inlineStr">
@@ -49877,34 +49873,30 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>몽크의아뜰리에</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>monks_atelier@naver.com</t>
-        </is>
-      </c>
+          <t>해오 붙임머리</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>0507-1305-7780</t>
+          <t>0507-1363-1231</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 성덕정길 33 1층</t>
+          <t>서울특별시 성동구 뚝섬로 391-3 1층</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monks_atelier</t>
+          <t>https://www.instagram.com/hae.o_shop?igsh=YXN2MndubmMzdzMw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -49939,13 +49931,13 @@
         </is>
       </c>
       <c r="P535" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Q535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R535" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="S535" t="inlineStr">
         <is>
@@ -49954,12 +49946,12 @@
       </c>
       <c r="T535" t="inlineStr">
         <is>
-          <t>1739286602</t>
+          <t>2013358828</t>
         </is>
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739286602</t>
+          <t>https://m.place.naver.com/place/2013358828</t>
         </is>
       </c>
       <c r="V535" t="inlineStr">
@@ -49971,34 +49963,30 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>펫살롱</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>petsalonk@naver.com</t>
-        </is>
-      </c>
+          <t>문선영미용실</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>0507-1380-2548</t>
+          <t>02-2292-5755</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 상왕십리동 16-4 텐즈힐몰 1층 112호</t>
+          <t>서울특별시 성동구 마조로 58</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>http://instagram.com/pet___salon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -50008,7 +49996,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -50029,17 +50017,17 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P536" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="Q536" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R536" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -50048,12 +50036,12 @@
       </c>
       <c r="T536" t="inlineStr">
         <is>
-          <t>1841418379</t>
+          <t>31398237</t>
         </is>
       </c>
       <c r="U536" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841418379</t>
+          <t>https://m.place.naver.com/place/31398237</t>
         </is>
       </c>
       <c r="V536" t="inlineStr">
@@ -50065,44 +50053,44 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>웨그앤코</t>
+          <t>굿띵서울 왕십리점</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>wagnco@naver.com</t>
+          <t>kkkjhcom@naver.com</t>
         </is>
       </c>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t>0507-1306-5999</t>
+          <t>0507-1364-9853</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 성덕정길 95 1층 웨그앤코</t>
+          <t>서울특별시 성동구 마조로5길 4-12 2층</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>http://www.wagnco.com</t>
+          <t>https://blog.naver.com/kkkjhcom</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -50127,13 +50115,13 @@
         </is>
       </c>
       <c r="P537" t="n">
-        <v>39</v>
+        <v>4421</v>
       </c>
       <c r="Q537" t="n">
-        <v>36</v>
+        <v>694</v>
       </c>
       <c r="R537" t="n">
-        <v>75</v>
+        <v>5115</v>
       </c>
       <c r="S537" t="inlineStr">
         <is>
@@ -50142,12 +50130,12 @@
       </c>
       <c r="T537" t="inlineStr">
         <is>
-          <t>1030363139</t>
+          <t>1012174775</t>
         </is>
       </c>
       <c r="U537" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030363139</t>
+          <t>https://m.place.naver.com/place/1012174775</t>
         </is>
       </c>
       <c r="V537" t="inlineStr">
@@ -50159,34 +50147,34 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>카밍독</t>
+          <t>뷰살롱 센트라스점</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>calmingdog_groom@naver.com</t>
+          <t>yeban4525@naver.com</t>
         </is>
       </c>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>0507-1416-8456</t>
+          <t>0507-1308-7998</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 마장로 137 401동 210호 (상가 2층입니다.)</t>
+          <t>서울특별시 성동구 왕십리로 410 센트라스상가 L동 지하1층 B121-1호</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/calmingdog_groom</t>
+          <t>http://www.instagram.com/view_yeban</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -50201,7 +50189,7 @@
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -50221,13 +50209,13 @@
         </is>
       </c>
       <c r="P538" t="n">
-        <v>8</v>
+        <v>1694</v>
       </c>
       <c r="Q538" t="n">
-        <v>36</v>
+        <v>364</v>
       </c>
       <c r="R538" t="n">
-        <v>44</v>
+        <v>2058</v>
       </c>
       <c r="S538" t="inlineStr">
         <is>
@@ -50236,12 +50224,12 @@
       </c>
       <c r="T538" t="inlineStr">
         <is>
-          <t>2052777832</t>
+          <t>1748281927</t>
         </is>
       </c>
       <c r="U538" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052777832</t>
+          <t>https://m.place.naver.com/place/1748281927</t>
         </is>
       </c>
       <c r="V538" t="inlineStr">
@@ -50253,44 +50241,36 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>도그마펫살롱</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>kimsajju@naver.com</t>
-        </is>
-      </c>
+          <t>선미용실</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>0507-1322-3258</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호로 127 상가동 19호</t>
+          <t>서울특별시 성동구 왕십리로22길 9</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/spmgTYg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
@@ -50306,22 +50286,22 @@
       <c r="M539" t="inlineStr"/>
       <c r="N539" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P539" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="Q539" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R539" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -50330,12 +50310,12 @@
       </c>
       <c r="T539" t="inlineStr">
         <is>
-          <t>1603545173</t>
+          <t>20834132</t>
         </is>
       </c>
       <c r="U539" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1603545173</t>
+          <t>https://m.place.naver.com/place/20834132</t>
         </is>
       </c>
       <c r="V539" t="inlineStr">
@@ -50347,34 +50327,30 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>묘그미</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>jakim112@naver.com</t>
-        </is>
-      </c>
+          <t>현대미용실</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>0507-1487-5828</t>
+          <t>02-2237-5302</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로6길 50 101동 1층 131호 묘그미</t>
+          <t>서울특별시 성동구 금호산2길 26-1</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cat_hugme/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -50384,7 +50360,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
@@ -50405,17 +50381,17 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P540" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Q540" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R540" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -50424,12 +50400,12 @@
       </c>
       <c r="T540" t="inlineStr">
         <is>
-          <t>2067069607</t>
+          <t>20899684</t>
         </is>
       </c>
       <c r="U540" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067069607</t>
+          <t>https://m.place.naver.com/place/20899684</t>
         </is>
       </c>
       <c r="V540" t="inlineStr">
@@ -50441,34 +50417,34 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>로이펫살롱</t>
+          <t>타마시헤어 성수점</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>chicpetsalon@naver.com</t>
+          <t>tamasihair@naver.com</t>
         </is>
       </c>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>0507-1494-0255</t>
+          <t>0507-1319-3684</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 행당로 76 한진노변상가 로이펫살롱 (CU옆)</t>
+          <t>서울특별시 성동구 연무장길 52 6층 601호</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/tamasihair_seongsu</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -50478,7 +50454,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -50499,17 +50475,17 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P541" t="n">
-        <v>12</v>
+        <v>1081</v>
       </c>
       <c r="Q541" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="R541" t="n">
-        <v>13</v>
+        <v>1131</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -50518,12 +50494,12 @@
       </c>
       <c r="T541" t="inlineStr">
         <is>
-          <t>1022354792</t>
+          <t>2026845386</t>
         </is>
       </c>
       <c r="U541" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1022354792</t>
+          <t>https://m.place.naver.com/place/2026845386</t>
         </is>
       </c>
       <c r="V541" t="inlineStr">
@@ -50535,29 +50511,29 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>수리,AS</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>컴퓨터수리데이터복구노트북AS센터</t>
+          <t>그라시아미용실</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>gasuro78@naver.com</t>
+          <t>eurobiketourblog@naver.com</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
-          <t>070-4534-9877</t>
+          <t>02-2294-2921</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 하왕십리동</t>
+          <t>서울특별시 성동구 고산자로 344</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -50597,13 +50573,13 @@
         </is>
       </c>
       <c r="P542" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q542" t="n">
         <v>0</v>
       </c>
       <c r="R542" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -50612,12 +50588,12 @@
       </c>
       <c r="T542" t="inlineStr">
         <is>
-          <t>1533060380</t>
+          <t>17895293</t>
         </is>
       </c>
       <c r="U542" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533060380</t>
+          <t>https://m.place.naver.com/place/17895293</t>
         </is>
       </c>
       <c r="V542" t="inlineStr">
@@ -50629,30 +50605,34 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>수리,AS</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>컴퓨터수리데이터복구노트북AS센터</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr"/>
+          <t>지투헤어</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>creamchocolatetart@naver.com</t>
+        </is>
+      </c>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
-          <t>070-4534-9561</t>
+          <t>02-2281-8994</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 마장동</t>
+          <t>서울특별시 성동구 장터길 11-1 1층</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/g2hair_/</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -50662,7 +50642,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
@@ -50683,17 +50663,17 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P543" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q543" t="n">
         <v>0</v>
       </c>
       <c r="R543" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
@@ -50702,12 +50682,12 @@
       </c>
       <c r="T543" t="inlineStr">
         <is>
-          <t>1513012509</t>
+          <t>1762687349</t>
         </is>
       </c>
       <c r="U543" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513012509</t>
+          <t>https://m.place.naver.com/place/1762687349</t>
         </is>
       </c>
       <c r="V543" t="inlineStr">
@@ -50719,49 +50699,53 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>수리,AS</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>컴퓨터수리데이터복구노트북AS센터</t>
+          <t>어낵 성수점</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>gasuro78@naver.com</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr"/>
+          <t>gkfn93@naver.com</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>aknacku@gmail.com</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>070-4534-0981</t>
+          <t>0507-1479-1270</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호동1가</t>
+          <t>서울특별시 성동구 성수일로1길 3 1-2층 어낵</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://aknack.kr/</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
@@ -50777,17 +50761,17 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P544" t="n">
-        <v>0</v>
+        <v>25938</v>
       </c>
       <c r="Q544" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="R544" t="n">
-        <v>0</v>
+        <v>26269</v>
       </c>
       <c r="S544" t="inlineStr">
         <is>
@@ -50796,12 +50780,12 @@
       </c>
       <c r="T544" t="inlineStr">
         <is>
-          <t>1855461744</t>
+          <t>1600445819</t>
         </is>
       </c>
       <c r="U544" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855461744</t>
+          <t>https://m.place.naver.com/place/1600445819</t>
         </is>
       </c>
       <c r="V544" t="inlineStr">
@@ -50813,49 +50797,53 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>아가도스 바버샵</t>
+          <t>베이바이허슬기 서울숲</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>agadosbarbershop@naver.com</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr"/>
+          <t>baybyheo@naver.com</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>0507-1331-9405</t>
+          <t>0507-1371-9391</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로4길 23-1 지하1층</t>
+          <t>서울특별시 성동구 서울숲4길 14 1, 2, 3, 4층</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/agadosbarbershop</t>
+          <t>http://booking.naver.com/booking/13/bizes/851268</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -50875,13 +50863,13 @@
         </is>
       </c>
       <c r="P545" t="n">
-        <v>374</v>
+        <v>6377</v>
       </c>
       <c r="Q545" t="n">
-        <v>22</v>
+        <v>570</v>
       </c>
       <c r="R545" t="n">
-        <v>396</v>
+        <v>6947</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -50890,12 +50878,12 @@
       </c>
       <c r="T545" t="inlineStr">
         <is>
-          <t>1266750251</t>
+          <t>1823742597</t>
         </is>
       </c>
       <c r="U545" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266750251</t>
+          <t>https://m.place.naver.com/place/1823742597</t>
         </is>
       </c>
       <c r="V545" t="inlineStr">
@@ -50907,21 +50895,25 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>마을이발관</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr"/>
+          <t>제이에이알헤어</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr"/>
       <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 용답중앙13길 6</t>
+          <t>서울특별시 성동구 왕십리로 410</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -50961,13 +50953,13 @@
         </is>
       </c>
       <c r="P546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q546" t="n">
         <v>0</v>
       </c>
       <c r="R546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -50976,12 +50968,12 @@
       </c>
       <c r="T546" t="inlineStr">
         <is>
-          <t>18798416</t>
+          <t>1333927130</t>
         </is>
       </c>
       <c r="U546" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18798416</t>
+          <t>https://m.place.naver.com/place/1333927130</t>
         </is>
       </c>
       <c r="V546" t="inlineStr">
@@ -50993,21 +50985,29 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>머리염색</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>장수이발</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr"/>
+          <t>오땡큐 금호4가동점</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>jys6622@naver.com</t>
+        </is>
+      </c>
       <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>02-2282-1784</t>
+        </is>
+      </c>
       <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 행당로6길 2</t>
+          <t>서울특별시 성동구 동호로2길 27-1</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -51047,13 +51047,13 @@
         </is>
       </c>
       <c r="P547" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="Q547" t="n">
         <v>0</v>
       </c>
       <c r="R547" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="S547" t="inlineStr">
         <is>
@@ -51062,12 +51062,12 @@
       </c>
       <c r="T547" t="inlineStr">
         <is>
-          <t>1129823457</t>
+          <t>1531156447</t>
         </is>
       </c>
       <c r="U547" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129823457</t>
+          <t>https://m.place.naver.com/place/1531156447</t>
         </is>
       </c>
       <c r="V547" t="inlineStr">
@@ -51079,21 +51079,29 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>머리염색</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>대중이발</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr"/>
+          <t>안나스파염색</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>saionsss@naver.com</t>
+        </is>
+      </c>
       <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>0507-1345-1513</t>
+        </is>
+      </c>
       <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 장터길 23-1</t>
+          <t>서울특별시 성동구 무학봉길 42 1층</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -51133,13 +51141,13 @@
         </is>
       </c>
       <c r="P548" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Q548" t="n">
         <v>0</v>
       </c>
       <c r="R548" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S548" t="inlineStr">
         <is>
@@ -51148,12 +51156,12 @@
       </c>
       <c r="T548" t="inlineStr">
         <is>
-          <t>20941751</t>
+          <t>1840237329</t>
         </is>
       </c>
       <c r="U548" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20941751</t>
+          <t>https://m.place.naver.com/place/1840237329</t>
         </is>
       </c>
       <c r="V548" t="inlineStr">
@@ -51165,35 +51173,39 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>머리염색</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>경선이발관</t>
+          <t>컬러드스파 왕십리센트라스점</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>bravomagazine@naver.com</t>
+          <t>7seven_avenue@naver.com</t>
         </is>
       </c>
       <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>0507-1347-6743</t>
+        </is>
+      </c>
       <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 하왕십리동 난계로 101-1</t>
+          <t>서울특별시 성동구 왕십리로 410 센트라스 상가 i동 139호 컬러드스파 왕십리센트라스점</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://colordespa.com/</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
@@ -51203,7 +51215,7 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -51214,22 +51226,22 @@
       <c r="M549" t="inlineStr"/>
       <c r="N549" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P549" t="n">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="Q549" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="R549" t="n">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="S549" t="inlineStr">
         <is>
@@ -51238,12 +51250,12 @@
       </c>
       <c r="T549" t="inlineStr">
         <is>
-          <t>34350674</t>
+          <t>2011248177</t>
         </is>
       </c>
       <c r="U549" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34350674</t>
+          <t>https://m.place.naver.com/place/2011248177</t>
         </is>
       </c>
       <c r="V549" t="inlineStr">
@@ -51255,34 +51267,34 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>머리염색</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>웰리마스</t>
+          <t>구피샵 금호점</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>wellytrip@naver.com</t>
+          <t>jiaesk97@naver.com</t>
         </is>
       </c>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>0507-1445-5548</t>
+          <t>02-2234-6001</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호로 78 1층</t>
+          <t>서울특별시 성동구 장터5길 3-1 구피샵</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/welleemars1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -51292,7 +51304,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
@@ -51313,17 +51325,17 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P550" t="n">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="Q550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R550" t="n">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -51332,12 +51344,12 @@
       </c>
       <c r="T550" t="inlineStr">
         <is>
-          <t>1000932759</t>
+          <t>1526743661</t>
         </is>
       </c>
       <c r="U550" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000932759</t>
+          <t>https://m.place.naver.com/place/1526743661</t>
         </is>
       </c>
       <c r="V550" t="inlineStr">
@@ -51349,30 +51361,34 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>금호이발</t>
+          <t>살롱비</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>hhhgym@naver.com</t>
+          <t>whas36@naver.com</t>
         </is>
       </c>
       <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>0507-1330-5602</t>
+        </is>
+      </c>
       <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 독서당로 284</t>
+          <t>서울특별시 성동구 금호로 170 2층 살롱비</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/whas36</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -51382,12 +51398,12 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -51407,13 +51423,13 @@
         </is>
       </c>
       <c r="P551" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="Q551" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R551" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -51422,12 +51438,12 @@
       </c>
       <c r="T551" t="inlineStr">
         <is>
-          <t>1921222032</t>
+          <t>1583270957</t>
         </is>
       </c>
       <c r="U551" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1921222032</t>
+          <t>https://m.place.naver.com/place/1583270957</t>
         </is>
       </c>
       <c r="V551" t="inlineStr">
@@ -51439,34 +51455,30 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용기기,재료</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>코헤드 바버샵</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>hwi86@naver.com</t>
-        </is>
-      </c>
+          <t>한진미용재료</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t>0507-1317-0721</t>
+          <t>0507-1338-9467</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 독서당로 184 1층 201호</t>
+          <t>서울특별시 성동구 왕십리로 322 1층 한진미용상사</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hwi86</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -51476,12 +51488,12 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -51497,17 +51509,17 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P552" t="n">
-        <v>765</v>
+        <v>275</v>
       </c>
       <c r="Q552" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="R552" t="n">
-        <v>813</v>
+        <v>276</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
@@ -51516,12 +51528,12 @@
       </c>
       <c r="T552" t="inlineStr">
         <is>
-          <t>1264734378</t>
+          <t>11561901</t>
         </is>
       </c>
       <c r="U552" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264734378</t>
+          <t>https://m.place.naver.com/place/11561901</t>
         </is>
       </c>
       <c r="V552" t="inlineStr">
@@ -51533,34 +51545,34 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>다운오디너리 바버샵</t>
+          <t>텐즈힐애견미용</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>angdunx@naver.com</t>
+          <t>ksj940412@naver.com</t>
         </is>
       </c>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>0507-1315-9321</t>
+          <t>0507-1321-7924</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호로 40 1F</t>
+          <t>서울특별시 성동구 마장로 137 텐즈힐 상가 1층 213동 114호</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/downodnrbarbershop</t>
+          <t>http://blog.naver.com/ksj940412</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -51575,7 +51587,7 @@
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
@@ -51595,13 +51607,13 @@
         </is>
       </c>
       <c r="P553" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="Q553" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="R553" t="n">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="S553" t="inlineStr">
         <is>
@@ -51610,12 +51622,12 @@
       </c>
       <c r="T553" t="inlineStr">
         <is>
-          <t>1618289318</t>
+          <t>1822735132</t>
         </is>
       </c>
       <c r="U553" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618289318</t>
+          <t>https://m.place.naver.com/place/1822735132</t>
         </is>
       </c>
       <c r="V553" t="inlineStr">
@@ -51627,30 +51639,30 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>신세대이발</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr"/>
+          <t>베이글버트그루밍</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>mnene@naver.com</t>
+        </is>
+      </c>
       <c r="D554" t="inlineStr"/>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>02-449-2838</t>
-        </is>
-      </c>
+      <c r="E554" t="inlineStr"/>
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호산2길 22-1</t>
+          <t>서울특별시 성동구 왕십리로4가길 2-9</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mnene</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -51660,12 +51672,12 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
@@ -51681,17 +51693,17 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P554" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q554" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="R554" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="S554" t="inlineStr">
         <is>
@@ -51700,12 +51712,12 @@
       </c>
       <c r="T554" t="inlineStr">
         <is>
-          <t>1500409362</t>
+          <t>1423888123</t>
         </is>
       </c>
       <c r="U554" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1500409362</t>
+          <t>https://m.place.naver.com/place/1423888123</t>
         </is>
       </c>
       <c r="V554" t="inlineStr">
@@ -51717,30 +51729,34 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>명동이발관</t>
+          <t>솜소밍</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>yesuw21@naver.com</t>
+          <t>somsoming__@naver.com</t>
         </is>
       </c>
       <c r="D555" t="inlineStr"/>
-      <c r="E555" t="inlineStr"/>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>0507-1367-7210</t>
+        </is>
+      </c>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 매봉길 6-1</t>
+          <t>서울특별시 성동구 고산자로14길 26 지웰홈스 왕십리 상가 1층 솜소밍</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/somsoming__</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -51750,12 +51766,12 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -51771,17 +51787,17 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P555" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q555" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R555" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="S555" t="inlineStr">
         <is>
@@ -51790,12 +51806,12 @@
       </c>
       <c r="T555" t="inlineStr">
         <is>
-          <t>20842226</t>
+          <t>1571638964</t>
         </is>
       </c>
       <c r="U555" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20842226</t>
+          <t>https://m.place.naver.com/place/1571638964</t>
         </is>
       </c>
       <c r="V555" t="inlineStr">
@@ -51807,30 +51823,34 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>중앙이발관</t>
+          <t>몽크의아뜰리에</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>rockview@naver.com</t>
+          <t>monks_atelier@naver.com</t>
         </is>
       </c>
       <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr"/>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>0507-1305-7780</t>
+        </is>
+      </c>
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 장터길 10-1</t>
+          <t>서울특별시 성동구 성덕정길 33 1층</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/monks_atelier</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -51840,7 +51860,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
@@ -51861,17 +51881,17 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P556" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R556" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S556" t="inlineStr">
         <is>
@@ -51880,12 +51900,12 @@
       </c>
       <c r="T556" t="inlineStr">
         <is>
-          <t>1796345366</t>
+          <t>1739286602</t>
         </is>
       </c>
       <c r="U556" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1796345366</t>
+          <t>https://m.place.naver.com/place/1739286602</t>
         </is>
       </c>
       <c r="V556" t="inlineStr">
@@ -51897,30 +51917,34 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>백제이발관</t>
+          <t>펫살롱</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>zmzpop@naver.com</t>
+          <t>petsalonk@naver.com</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
-      <c r="E557" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>0507-1380-2548</t>
+        </is>
+      </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 용답중앙27길 3</t>
+          <t>서울특별시 성동구 상왕십리동 16-4 텐즈힐몰 1층 112호</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/pet___salon</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -51930,7 +51954,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
@@ -51951,17 +51975,17 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P557" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q557" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R557" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S557" t="inlineStr">
         <is>
@@ -51970,12 +51994,12 @@
       </c>
       <c r="T557" t="inlineStr">
         <is>
-          <t>1642717005</t>
+          <t>1841418379</t>
         </is>
       </c>
       <c r="U557" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642717005</t>
+          <t>https://m.place.naver.com/place/1841418379</t>
         </is>
       </c>
       <c r="V557" t="inlineStr">
@@ -51987,35 +52011,39 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>나이스컷</t>
+          <t>웨그앤코</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>varocoffee@naver.com</t>
+          <t>wagnco@naver.com</t>
         </is>
       </c>
       <c r="D558" t="inlineStr"/>
-      <c r="E558" t="inlineStr"/>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>0507-1306-5999</t>
+        </is>
+      </c>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 광나루로11길 38</t>
+          <t>서울특별시 성동구 성덕정길 95 1층 웨그앤코</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.wagnco.com</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -52025,7 +52053,7 @@
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
@@ -52041,17 +52069,17 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P558" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q558" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R558" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S558" t="inlineStr">
         <is>
@@ -52060,12 +52088,12 @@
       </c>
       <c r="T558" t="inlineStr">
         <is>
-          <t>1273364632</t>
+          <t>1030363139</t>
         </is>
       </c>
       <c r="U558" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273364632</t>
+          <t>https://m.place.naver.com/place/1030363139</t>
         </is>
       </c>
       <c r="V558" t="inlineStr">
@@ -52077,30 +52105,34 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>성산이발관</t>
+          <t>카밍독</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>lmk47074@naver.com</t>
+          <t>calmingdog_groom@naver.com</t>
         </is>
       </c>
       <c r="D559" t="inlineStr"/>
-      <c r="E559" t="inlineStr"/>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>0507-1416-8456</t>
+        </is>
+      </c>
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 금호산길 57</t>
+          <t>서울특별시 성동구 마장로 137 401동 210호 (상가 2층입니다.)</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/calmingdog_groom</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -52110,12 +52142,12 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -52131,17 +52163,17 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P559" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q559" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R559" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S559" t="inlineStr">
         <is>
@@ -52150,12 +52182,12 @@
       </c>
       <c r="T559" t="inlineStr">
         <is>
-          <t>1904056932</t>
+          <t>2052777832</t>
         </is>
       </c>
       <c r="U559" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1904056932</t>
+          <t>https://m.place.naver.com/place/2052777832</t>
         </is>
       </c>
       <c r="V559" t="inlineStr">
@@ -52167,44 +52199,44 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>보석이용원</t>
+          <t>도그마펫살롱</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>a-life-of-han@naver.com</t>
+          <t>kimsajju@naver.com</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
-          <t>02-2299-6874</t>
+          <t>0507-1322-3258</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 고산자로10길 22-12</t>
+          <t>서울특별시 성동구 금호로 127 상가동 19호</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/spmgTYg</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
@@ -52220,22 +52252,22 @@
       <c r="M560" t="inlineStr"/>
       <c r="N560" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P560" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="Q560" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R560" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="S560" t="inlineStr">
         <is>
@@ -52244,12 +52276,12 @@
       </c>
       <c r="T560" t="inlineStr">
         <is>
-          <t>1067073800</t>
+          <t>1603545173</t>
         </is>
       </c>
       <c r="U560" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1067073800</t>
+          <t>https://m.place.naver.com/place/1603545173</t>
         </is>
       </c>
       <c r="V560" t="inlineStr">
@@ -52261,30 +52293,34 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>상가이용원</t>
+          <t>묘그미</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>ccchoich@naver.com</t>
+          <t>jakim112@naver.com</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
-      <c r="E561" t="inlineStr"/>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>0507-1487-5828</t>
+        </is>
+      </c>
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 자동차시장1길 70</t>
+          <t>서울특별시 성동구 무학로6길 50 101동 1층 131호 묘그미</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cat_hugme/</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -52294,7 +52330,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -52315,17 +52351,17 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P561" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="Q561" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R561" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="S561" t="inlineStr">
         <is>
@@ -52334,12 +52370,12 @@
       </c>
       <c r="T561" t="inlineStr">
         <is>
-          <t>1669839361</t>
+          <t>2067069607</t>
         </is>
       </c>
       <c r="U561" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669839361</t>
+          <t>https://m.place.naver.com/place/2067069607</t>
         </is>
       </c>
       <c r="V561" t="inlineStr">
@@ -52351,38 +52387,34 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>오클리먼33바버샵 성수점</t>
+          <t>로이펫살롱</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>damiok@naver.com</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>ocleremon33@gmail.com</t>
-        </is>
-      </c>
+          <t>chicpetsalon@naver.com</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
-          <t>0507-1328-6076</t>
+          <t>0507-1494-0255</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 연무장5가길 7 현대테라스타워 1층 로비옆 132호</t>
+          <t>서울특별시 성동구 행당로 76 한진노변상가 로이펫살롱 (CU옆)</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>https://youtube.com/ocleremon33</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -52392,7 +52424,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -52413,17 +52445,17 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P562" t="n">
-        <v>422</v>
+        <v>12</v>
       </c>
       <c r="Q562" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R562" t="n">
-        <v>439</v>
+        <v>13</v>
       </c>
       <c r="S562" t="inlineStr">
         <is>
@@ -52432,12 +52464,12 @@
       </c>
       <c r="T562" t="inlineStr">
         <is>
-          <t>1175810932</t>
+          <t>1022354792</t>
         </is>
       </c>
       <c r="U562" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175810932</t>
+          <t>https://m.place.naver.com/place/1022354792</t>
         </is>
       </c>
       <c r="V562" t="inlineStr">
@@ -52449,34 +52481,30 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>반려동물미용</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>407바버샵</t>
+          <t>마이뷰티독</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>hymdau0707@naver.com</t>
+          <t>mbd001@naver.com</t>
         </is>
       </c>
       <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr">
-        <is>
-          <t>0507-1407-0408</t>
-        </is>
-      </c>
+      <c r="E563" t="inlineStr"/>
       <c r="F563" t="inlineStr"/>
       <c r="G563" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로 273-12 1층</t>
+          <t>서울특별시 성동구 마장로 137</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sssube</t>
+          <t>http://blog.naver.com/mbd001</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -52491,7 +52519,7 @@
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
@@ -52507,17 +52535,17 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P563" t="n">
-        <v>1073</v>
+        <v>35</v>
       </c>
       <c r="Q563" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="R563" t="n">
-        <v>1153</v>
+        <v>37</v>
       </c>
       <c r="S563" t="inlineStr">
         <is>
@@ -52526,12 +52554,12 @@
       </c>
       <c r="T563" t="inlineStr">
         <is>
-          <t>1798214230</t>
+          <t>650238092</t>
         </is>
       </c>
       <c r="U563" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798214230</t>
+          <t>https://m.place.naver.com/place/650238092</t>
         </is>
       </c>
       <c r="V563" t="inlineStr">
@@ -52543,34 +52571,34 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>수리,AS</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>디케이바버샵</t>
+          <t>컴퓨터수리데이터복구노트북AS센터</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>dk1603@naver.com</t>
+          <t>gasuro78@naver.com</t>
         </is>
       </c>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr">
         <is>
-          <t>0507-1372-0951</t>
+          <t>070-4534-9877</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
       <c r="G564" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로6길 50 쉐르빌아파트 1층 상가 145호 디케이바버샵</t>
+          <t>서울특별시 성동구 하왕십리동</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dk1603</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -52580,12 +52608,12 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -52601,17 +52629,17 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P564" t="n">
-        <v>7713</v>
+        <v>0</v>
       </c>
       <c r="Q564" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="R564" t="n">
-        <v>7825</v>
+        <v>0</v>
       </c>
       <c r="S564" t="inlineStr">
         <is>
@@ -52620,12 +52648,12 @@
       </c>
       <c r="T564" t="inlineStr">
         <is>
-          <t>1105263082</t>
+          <t>1533060380</t>
         </is>
       </c>
       <c r="U564" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105263082</t>
+          <t>https://m.place.naver.com/place/1533060380</t>
         </is>
       </c>
       <c r="V564" t="inlineStr">
@@ -52637,25 +52665,25 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>수리,AS</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>정희이용원</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>drawing0123@naver.com</t>
-        </is>
-      </c>
+          <t>컴퓨터수리데이터복구노트북AS센터</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>070-4534-9561</t>
+        </is>
+      </c>
       <c r="F565" t="inlineStr"/>
       <c r="G565" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 성수이로7가길 24</t>
+          <t>서울특별시 성동구 마장동</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -52695,13 +52723,13 @@
         </is>
       </c>
       <c r="P565" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q565" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R565" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S565" t="inlineStr">
         <is>
@@ -52710,12 +52738,12 @@
       </c>
       <c r="T565" t="inlineStr">
         <is>
-          <t>18795863</t>
+          <t>1513012509</t>
         </is>
       </c>
       <c r="U565" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18795863</t>
+          <t>https://m.place.naver.com/place/1513012509</t>
         </is>
       </c>
       <c r="V565" t="inlineStr">
@@ -52727,29 +52755,29 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>수리,AS</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>대성이발관</t>
+          <t>컴퓨터수리데이터복구노트북AS센터</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>bddjsj@naver.com</t>
+          <t>gasuro78@naver.com</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>02-2281-7454</t>
+          <t>070-4534-0981</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 독서당로 228</t>
+          <t>서울특별시 성동구 금호동1가</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -52792,10 +52820,10 @@
         <v>0</v>
       </c>
       <c r="Q566" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R566" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -52804,12 +52832,12 @@
       </c>
       <c r="T566" t="inlineStr">
         <is>
-          <t>20918987</t>
+          <t>1855461744</t>
         </is>
       </c>
       <c r="U566" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20918987</t>
+          <t>https://m.place.naver.com/place/1855461744</t>
         </is>
       </c>
       <c r="V566" t="inlineStr">
@@ -52826,29 +52854,29 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>언코우트 성수점</t>
+          <t>아가도스 바버샵</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>w5695daum@naver.com</t>
+          <t>agadosbarbershop@naver.com</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr">
         <is>
-          <t>0507-1423-1409</t>
+          <t>0507-1331-9405</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
       <c r="G567" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 상원12길 20-14 2층</t>
+          <t>서울특별시 성동구 왕십리로4길 23-1 지하1층</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/agadosbarbershop</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -52858,12 +52886,12 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -52879,17 +52907,17 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P567" t="n">
-        <v>246</v>
+        <v>374</v>
       </c>
       <c r="Q567" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="R567" t="n">
-        <v>282</v>
+        <v>396</v>
       </c>
       <c r="S567" t="inlineStr">
         <is>
@@ -52898,12 +52926,12 @@
       </c>
       <c r="T567" t="inlineStr">
         <is>
-          <t>1728575115</t>
+          <t>1266750251</t>
         </is>
       </c>
       <c r="U567" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1728575115</t>
+          <t>https://m.place.naver.com/place/1266750251</t>
         </is>
       </c>
       <c r="V567" t="inlineStr">
@@ -52920,7 +52948,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>모범이용원</t>
+          <t>마을이발관</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -52929,7 +52957,7 @@
       <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 고산자로 293</t>
+          <t>서울특별시 성동구 용답중앙13길 6</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -52969,13 +52997,13 @@
         </is>
       </c>
       <c r="P568" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q568" t="n">
         <v>0</v>
       </c>
       <c r="R568" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S568" t="inlineStr">
         <is>
@@ -52984,12 +53012,12 @@
       </c>
       <c r="T568" t="inlineStr">
         <is>
-          <t>20926535</t>
+          <t>18798416</t>
         </is>
       </c>
       <c r="U568" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20926535</t>
+          <t>https://m.place.naver.com/place/18798416</t>
         </is>
       </c>
       <c r="V568" t="inlineStr">
@@ -53006,20 +53034,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>남미이용원</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>0547383@naver.com</t>
-        </is>
-      </c>
+          <t>장수이발</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr"/>
       <c r="G569" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로12길 2</t>
+          <t>서울특별시 성동구 행당로6길 2</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -53059,13 +53083,13 @@
         </is>
       </c>
       <c r="P569" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q569" t="n">
         <v>0</v>
       </c>
       <c r="R569" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S569" t="inlineStr">
         <is>
@@ -53074,12 +53098,12 @@
       </c>
       <c r="T569" t="inlineStr">
         <is>
-          <t>1176772928</t>
+          <t>1129823457</t>
         </is>
       </c>
       <c r="U569" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176772928</t>
+          <t>https://m.place.naver.com/place/1129823457</t>
         </is>
       </c>
       <c r="V569" t="inlineStr">
@@ -53096,25 +53120,21 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>커터번치바버샵</t>
+          <t>대중이발</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>0507-1490-0321</t>
-        </is>
-      </c>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 성덕정길 80 1F 커터번치바버샵</t>
+          <t>서울특별시 성동구 장터길 23-1</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/cutterbunchbarbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -53124,7 +53144,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -53145,17 +53165,17 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P570" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q570" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R570" t="n">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="S570" t="inlineStr">
         <is>
@@ -53164,12 +53184,12 @@
       </c>
       <c r="T570" t="inlineStr">
         <is>
-          <t>1369876380</t>
+          <t>20941751</t>
         </is>
       </c>
       <c r="U570" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369876380</t>
+          <t>https://m.place.naver.com/place/20941751</t>
         </is>
       </c>
       <c r="V570" t="inlineStr">
@@ -53186,20 +53206,20 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>길손이발</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr"/>
+          <t>경선이발관</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>bravomagazine@naver.com</t>
+        </is>
+      </c>
       <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>02-2294-5497</t>
-        </is>
-      </c>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
       <c r="G571" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 사근동10길 2-6</t>
+          <t>서울특별시 성동구 하왕십리동 난계로 101-1</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -53239,13 +53259,13 @@
         </is>
       </c>
       <c r="P571" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q571" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R571" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S571" t="inlineStr">
         <is>
@@ -53254,12 +53274,12 @@
       </c>
       <c r="T571" t="inlineStr">
         <is>
-          <t>34349280</t>
+          <t>34350674</t>
         </is>
       </c>
       <c r="U571" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34349280</t>
+          <t>https://m.place.naver.com/place/34350674</t>
         </is>
       </c>
       <c r="V571" t="inlineStr">
@@ -53276,25 +53296,29 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>왕십리이용원</t>
+          <t>웰리마스</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>bepachangup@naver.com</t>
+          <t>wellytrip@naver.com</t>
         </is>
       </c>
       <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>0507-1445-5548</t>
+        </is>
+      </c>
       <c r="F572" t="inlineStr"/>
       <c r="G572" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학봉15길 4</t>
+          <t>서울특별시 성동구 금호로 78 1층</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/welleemars1</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -53304,7 +53328,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
@@ -53325,17 +53349,17 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P572" t="n">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="Q572" t="n">
         <v>0</v>
       </c>
       <c r="R572" t="n">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="S572" t="inlineStr">
         <is>
@@ -53344,12 +53368,12 @@
       </c>
       <c r="T572" t="inlineStr">
         <is>
-          <t>1166001577</t>
+          <t>1000932759</t>
         </is>
       </c>
       <c r="U572" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166001577</t>
+          <t>https://m.place.naver.com/place/1000932759</t>
         </is>
       </c>
       <c r="V572" t="inlineStr">
@@ -53366,12 +53390,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>로커빌리 바버샵</t>
+          <t>금호이발</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>jeonghaana@naver.com</t>
+          <t>hhhgym@naver.com</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -53379,27 +53403,27 @@
       <c r="F573" t="inlineStr"/>
       <c r="G573" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학봉15가길 4 1층 로커빌리 바버샵</t>
+          <t>서울특별시 성동구 독서당로 284</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rockabilly_barbershop_seoul/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
@@ -53415,17 +53439,17 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P573" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Q573" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R573" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="S573" t="inlineStr">
         <is>
@@ -53434,12 +53458,12 @@
       </c>
       <c r="T573" t="inlineStr">
         <is>
-          <t>1353159243</t>
+          <t>1921222032</t>
         </is>
       </c>
       <c r="U573" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353159243</t>
+          <t>https://m.place.naver.com/place/1921222032</t>
         </is>
       </c>
       <c r="V573" t="inlineStr">
@@ -53456,25 +53480,29 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>고향이발</t>
+          <t>코헤드 바버샵</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>tlsduswjd88@naver.com</t>
+          <t>hwi86@naver.com</t>
         </is>
       </c>
       <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>0507-1317-0721</t>
+        </is>
+      </c>
       <c r="F574" t="inlineStr"/>
       <c r="G574" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로28길 8-1</t>
+          <t>서울특별시 성동구 독서당로 184 1층 201호</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hwi86</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -53484,12 +53512,12 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
@@ -53505,17 +53533,17 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P574" t="n">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="Q574" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="R574" t="n">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="S574" t="inlineStr">
         <is>
@@ -53524,12 +53552,12 @@
       </c>
       <c r="T574" t="inlineStr">
         <is>
-          <t>1912331069</t>
+          <t>1264734378</t>
         </is>
       </c>
       <c r="U574" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1912331069</t>
+          <t>https://m.place.naver.com/place/1264734378</t>
         </is>
       </c>
       <c r="V574" t="inlineStr">
@@ -53546,25 +53574,29 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>마을이용원</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr"/>
+          <t>다운오디너리 바버샵</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>angdunx@naver.com</t>
+        </is>
+      </c>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr">
         <is>
-          <t>02-2234-6578</t>
+          <t>0507-1315-9321</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
       <c r="G575" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무수막길 86 마을</t>
+          <t>서울특별시 성동구 금호로 40 1F</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/downodnrbarbershop</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -53574,7 +53606,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K575" t="inlineStr">
@@ -53595,17 +53627,17 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P575" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="Q575" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R575" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="S575" t="inlineStr">
         <is>
@@ -53614,12 +53646,12 @@
       </c>
       <c r="T575" t="inlineStr">
         <is>
-          <t>1924289091</t>
+          <t>1618289318</t>
         </is>
       </c>
       <c r="U575" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924289091</t>
+          <t>https://m.place.naver.com/place/1618289318</t>
         </is>
       </c>
       <c r="V575" t="inlineStr">
@@ -53636,16 +53668,20 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>모모이발관</t>
+          <t>신세대이발</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>02-449-2838</t>
+        </is>
+      </c>
       <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 광나루로11길 41</t>
+          <t>서울특별시 성동구 금호산2길 22-1</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -53685,13 +53721,13 @@
         </is>
       </c>
       <c r="P576" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q576" t="n">
         <v>0</v>
       </c>
       <c r="R576" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S576" t="inlineStr">
         <is>
@@ -53700,12 +53736,12 @@
       </c>
       <c r="T576" t="inlineStr">
         <is>
-          <t>20850042</t>
+          <t>1500409362</t>
         </is>
       </c>
       <c r="U576" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20850042</t>
+          <t>https://m.place.naver.com/place/1500409362</t>
         </is>
       </c>
       <c r="V576" t="inlineStr">
@@ -53722,16 +53758,20 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>영락이용원</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr"/>
+          <t>명동이발관</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>yesuw21@naver.com</t>
+        </is>
+      </c>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 살곶이2길 28-1</t>
+          <t>서울특별시 성동구 매봉길 6-1</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -53774,10 +53814,10 @@
         <v>0</v>
       </c>
       <c r="Q577" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R577" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S577" t="inlineStr">
         <is>
@@ -53786,12 +53826,12 @@
       </c>
       <c r="T577" t="inlineStr">
         <is>
-          <t>2143337389</t>
+          <t>20842226</t>
         </is>
       </c>
       <c r="U577" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2143337389</t>
+          <t>https://m.place.naver.com/place/20842226</t>
         </is>
       </c>
       <c r="V577" t="inlineStr">
@@ -53808,29 +53848,25 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>오드볼</t>
+          <t>중앙이발관</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>ynarang@naver.com</t>
+          <t>rockview@naver.com</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>0507-1347-9809</t>
-        </is>
-      </c>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="inlineStr"/>
       <c r="G578" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로4길 9 1층</t>
+          <t>서울특별시 성동구 장터길 10-1</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oddball.kr?igsh=ZmQ0NmN4Y3cyOXZk&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -53840,7 +53876,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
@@ -53861,17 +53897,17 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P578" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="Q578" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R578" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="S578" t="inlineStr">
         <is>
@@ -53880,12 +53916,12 @@
       </c>
       <c r="T578" t="inlineStr">
         <is>
-          <t>1370783117</t>
+          <t>1796345366</t>
         </is>
       </c>
       <c r="U578" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370783117</t>
+          <t>https://m.place.naver.com/place/1796345366</t>
         </is>
       </c>
       <c r="V578" t="inlineStr">
@@ -53902,24 +53938,20 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>대성이발관</t>
+          <t>백제이발관</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>bddjsj@naver.com</t>
+          <t>zmzpop@naver.com</t>
         </is>
       </c>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>02-2292-2352</t>
-        </is>
-      </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="inlineStr"/>
       <c r="G579" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 독서당로60길 6</t>
+          <t>서울특별시 성동구 용답중앙27길 3</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -53959,13 +53991,13 @@
         </is>
       </c>
       <c r="P579" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q579" t="n">
         <v>0</v>
       </c>
       <c r="R579" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S579" t="inlineStr">
         <is>
@@ -53974,12 +54006,12 @@
       </c>
       <c r="T579" t="inlineStr">
         <is>
-          <t>17904873</t>
+          <t>1642717005</t>
         </is>
       </c>
       <c r="U579" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17904873</t>
+          <t>https://m.place.naver.com/place/1642717005</t>
         </is>
       </c>
       <c r="V579" t="inlineStr">
@@ -53996,29 +54028,25 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>고도 바버샵</t>
+          <t>나이스컷</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>chobani9@naver.com</t>
+          <t>varocoffee@naver.com</t>
         </is>
       </c>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>0507-1312-1034</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무수막길 41-4 1층 고도</t>
+          <t>서울특별시 성동구 광나루로11길 38</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/godo_barbershop/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -54028,7 +54056,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
@@ -54049,17 +54077,17 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P580" t="n">
-        <v>1591</v>
+        <v>0</v>
       </c>
       <c r="Q580" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="R580" t="n">
-        <v>1721</v>
+        <v>0</v>
       </c>
       <c r="S580" t="inlineStr">
         <is>
@@ -54068,12 +54096,12 @@
       </c>
       <c r="T580" t="inlineStr">
         <is>
-          <t>1979339399</t>
+          <t>1273364632</t>
         </is>
       </c>
       <c r="U580" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1979339399</t>
+          <t>https://m.place.naver.com/place/1273364632</t>
         </is>
       </c>
       <c r="V580" t="inlineStr">
@@ -54090,29 +54118,25 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>녹크바버샵</t>
+          <t>성산이발관</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>kimhn0810@naver.com</t>
+          <t>lmk47074@naver.com</t>
         </is>
       </c>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>02-2292-2772</t>
-        </is>
-      </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="inlineStr"/>
       <c r="G581" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 청계천로10나길 77 1층 녹크바버샵</t>
+          <t>서울특별시 성동구 금호산길 57</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/NOKKBARBERSHOP</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -54122,7 +54146,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
@@ -54143,17 +54167,17 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P581" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="Q581" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="R581" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="S581" t="inlineStr">
         <is>
@@ -54162,12 +54186,12 @@
       </c>
       <c r="T581" t="inlineStr">
         <is>
-          <t>1357253033</t>
+          <t>1904056932</t>
         </is>
       </c>
       <c r="U581" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1357253033</t>
+          <t>https://m.place.naver.com/place/1904056932</t>
         </is>
       </c>
       <c r="V581" t="inlineStr">
@@ -54184,29 +54208,29 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>디투디바버샵</t>
+          <t>보석이용원</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>dubarber@naver.com</t>
+          <t>a-life-of-han@naver.com</t>
         </is>
       </c>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>0507-1336-2981</t>
+          <t>02-2299-6874</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로6길 50 101동 141호</t>
+          <t>서울특별시 성동구 고산자로10길 22-12</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dubarber</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -54216,12 +54240,12 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L582" t="inlineStr">
@@ -54237,17 +54261,17 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P582" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="Q582" t="n">
         <v>0</v>
       </c>
       <c r="R582" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="S582" t="inlineStr">
         <is>
@@ -54256,12 +54280,12 @@
       </c>
       <c r="T582" t="inlineStr">
         <is>
-          <t>2009204909</t>
+          <t>1067073800</t>
         </is>
       </c>
       <c r="U582" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009204909</t>
+          <t>https://m.place.naver.com/place/1067073800</t>
         </is>
       </c>
       <c r="V582" t="inlineStr">
@@ -54278,12 +54302,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>중앙이발관</t>
+          <t>상가이용원</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>rockview@naver.com</t>
+          <t>ccchoich@naver.com</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
@@ -54291,7 +54315,7 @@
       <c r="F583" t="inlineStr"/>
       <c r="G583" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 왕십리로21길 30</t>
+          <t>서울특별시 성동구 자동차시장1길 70</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -54331,13 +54355,13 @@
         </is>
       </c>
       <c r="P583" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q583" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R583" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S583" t="inlineStr">
         <is>
@@ -54346,12 +54370,12 @@
       </c>
       <c r="T583" t="inlineStr">
         <is>
-          <t>1840672869</t>
+          <t>1669839361</t>
         </is>
       </c>
       <c r="U583" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840672869</t>
+          <t>https://m.place.naver.com/place/1669839361</t>
         </is>
       </c>
       <c r="V583" t="inlineStr">
@@ -54363,34 +54387,38 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>넘버인테리어</t>
+          <t>오클리먼33바버샵 성수점</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>kare-korea@naver.com</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr"/>
+          <t>damiok@naver.com</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>ocleremon33@gmail.com</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>0507-1413-4356</t>
+          <t>0507-1328-6076</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 매봉길 15</t>
+          <t>서울특별시 성동구 연무장5가길 7 현대테라스타워 1층 로비옆 132호</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/ocleremon33</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -54400,7 +54428,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
@@ -54421,17 +54449,17 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P584" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="Q584" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R584" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="S584" t="inlineStr">
         <is>
@@ -54440,12 +54468,12 @@
       </c>
       <c r="T584" t="inlineStr">
         <is>
-          <t>1446473953</t>
+          <t>1175810932</t>
         </is>
       </c>
       <c r="U584" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446473953</t>
+          <t>https://m.place.naver.com/place/1175810932</t>
         </is>
       </c>
       <c r="V584" t="inlineStr">
@@ -54457,34 +54485,34 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>감성인테리어</t>
+          <t>407바버샵</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>damda001@naver.com</t>
+          <t>hymdau0707@naver.com</t>
         </is>
       </c>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr">
         <is>
-          <t>0507-1328-4321</t>
+          <t>0507-1407-0408</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
       <c r="G585" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 무학로2길 30</t>
+          <t>서울특별시 성동구 왕십리로 273-12 1층</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sssube</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -54494,7 +54522,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K585" t="inlineStr">
@@ -54515,17 +54543,17 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P585" t="n">
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="Q585" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R585" t="n">
-        <v>0</v>
+        <v>1153</v>
       </c>
       <c r="S585" t="inlineStr">
         <is>
@@ -54534,12 +54562,12 @@
       </c>
       <c r="T585" t="inlineStr">
         <is>
-          <t>1198525354</t>
+          <t>1798214230</t>
         </is>
       </c>
       <c r="U585" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198525354</t>
+          <t>https://m.place.naver.com/place/1798214230</t>
         </is>
       </c>
       <c r="V585" t="inlineStr">
@@ -54551,34 +54579,34 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>다준디자인</t>
+          <t>디케이바버샵</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>khb960@naver.com</t>
+          <t>dk1603@naver.com</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
       <c r="E586" t="inlineStr">
         <is>
-          <t>0507-1429-5607</t>
+          <t>0507-1372-0951</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 마조로15가길 23</t>
+          <t>서울특별시 성동구 무학로6길 50 쉐르빌아파트 1층 상가 145호 디케이바버샵</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/khb960</t>
+          <t>https://blog.naver.com/dk1603</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -54609,34 +54637,2132 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P586" t="n">
+        <v>7713</v>
+      </c>
+      <c r="Q586" t="n">
+        <v>112</v>
+      </c>
+      <c r="R586" t="n">
+        <v>7825</v>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>1105263082</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105263082</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>정희이용원</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>drawing0123@naver.com</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr"/>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수이로7가길 24</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr"/>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P587" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q587" t="n">
+        <v>4</v>
+      </c>
+      <c r="R587" t="n">
+        <v>6</v>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>18795863</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18795863</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>대성이발관</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>bddjsj@naver.com</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr"/>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>02-2281-7454</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 228</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr"/>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P588" t="n">
         <v>0</v>
       </c>
-      <c r="Q586" t="n">
+      <c r="Q588" t="n">
+        <v>1</v>
+      </c>
+      <c r="R588" t="n">
+        <v>1</v>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>20918987</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20918987</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>언코우트 성수점</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>w5695daum@naver.com</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr"/>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>0507-1423-1409</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원12길 20-14 2층</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr"/>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P589" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q589" t="n">
+        <v>36</v>
+      </c>
+      <c r="R589" t="n">
+        <v>282</v>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>1728575115</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1728575115</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>모범이용원</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr"/>
+      <c r="D590" t="inlineStr"/>
+      <c r="E590" t="inlineStr"/>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 293</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr"/>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P590" t="n">
         <v>0</v>
       </c>
-      <c r="R586" t="n">
+      <c r="Q590" t="n">
         <v>0</v>
       </c>
-      <c r="S586" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T586" t="inlineStr">
+      <c r="R590" t="n">
+        <v>0</v>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>20926535</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20926535</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>남미이용원</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>0547383@naver.com</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로12길 2</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr"/>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P591" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>0</v>
+      </c>
+      <c r="R591" t="n">
+        <v>4</v>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>1176772928</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176772928</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>커터번치바버샵</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr"/>
+      <c r="D592" t="inlineStr"/>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>0507-1490-0321</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성덕정길 80 1F 커터번치바버샵</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/cutterbunchbarbershop</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr"/>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P592" t="n">
+        <v>815</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>7</v>
+      </c>
+      <c r="R592" t="n">
+        <v>822</v>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>1369876380</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1369876380</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>길손이발</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr"/>
+      <c r="D593" t="inlineStr"/>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>02-2294-5497</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 사근동10길 2-6</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr"/>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P593" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q593" t="n">
+        <v>1</v>
+      </c>
+      <c r="R593" t="n">
+        <v>1</v>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>34349280</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34349280</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>왕십리이용원</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>bepachangup@naver.com</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+      <c r="E594" t="inlineStr"/>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학봉15길 4</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr"/>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P594" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q594" t="n">
+        <v>0</v>
+      </c>
+      <c r="R594" t="n">
+        <v>2</v>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>1166001577</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1166001577</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>로커빌리 바버샵</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>jeonghaana@naver.com</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+      <c r="E595" t="inlineStr"/>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학봉15가길 4 1층 로커빌리 바버샵</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rockabilly_barbershop_seoul/</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr"/>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P595" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q595" t="n">
+        <v>4</v>
+      </c>
+      <c r="R595" t="n">
+        <v>214</v>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>1353159243</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1353159243</t>
+        </is>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>고향이발</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>tlsduswjd88@naver.com</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr"/>
+      <c r="E596" t="inlineStr"/>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로28길 8-1</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr"/>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P596" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q596" t="n">
+        <v>0</v>
+      </c>
+      <c r="R596" t="n">
+        <v>0</v>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>1912331069</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1912331069</t>
+        </is>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>마을이용원</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr"/>
+      <c r="D597" t="inlineStr"/>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>02-2234-6578</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무수막길 86 마을</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr"/>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P597" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>1</v>
+      </c>
+      <c r="R597" t="n">
+        <v>2</v>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>1924289091</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924289091</t>
+        </is>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>모모이발관</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
+      <c r="D598" t="inlineStr"/>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 광나루로11길 41</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr"/>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P598" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q598" t="n">
+        <v>0</v>
+      </c>
+      <c r="R598" t="n">
+        <v>2</v>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>20850042</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20850042</t>
+        </is>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>영락이용원</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr"/>
+      <c r="D599" t="inlineStr"/>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 살곶이2길 28-1</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr"/>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P599" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>0</v>
+      </c>
+      <c r="R599" t="n">
+        <v>0</v>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>2143337389</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2143337389</t>
+        </is>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>오드볼</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>ynarang@naver.com</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>0507-1347-9809</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로4길 9 1층</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oddball.kr?igsh=ZmQ0NmN4Y3cyOXZk&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr"/>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P600" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q600" t="n">
+        <v>20</v>
+      </c>
+      <c r="R600" t="n">
+        <v>119</v>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>1370783117</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370783117</t>
+        </is>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>대성이발관</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>bddjsj@naver.com</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr"/>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>02-2292-2352</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로60길 6</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr"/>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P601" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>0</v>
+      </c>
+      <c r="R601" t="n">
+        <v>2</v>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>17904873</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17904873</t>
+        </is>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>고도 바버샵</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>chobani9@naver.com</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>0507-1312-1034</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무수막길 41-4 1층 고도</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/godo_barbershop/</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr"/>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P602" t="n">
+        <v>1591</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>130</v>
+      </c>
+      <c r="R602" t="n">
+        <v>1721</v>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>1979339399</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1979339399</t>
+        </is>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>녹크바버샵</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>kimhn0810@naver.com</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>02-2292-2772</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 청계천로10나길 77 1층 녹크바버샵</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/NOKKBARBERSHOP</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr"/>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P603" t="n">
+        <v>408</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>54</v>
+      </c>
+      <c r="R603" t="n">
+        <v>462</v>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>1357253033</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1357253033</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>디투디바버샵</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>dubarber@naver.com</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>0507-1336-2981</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로6길 50 101동 141호</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dubarber</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr"/>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P604" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>0</v>
+      </c>
+      <c r="R604" t="n">
+        <v>134</v>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>2009204909</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2009204909</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>중앙이발관</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>rockview@naver.com</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr"/>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로21길 30</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr"/>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P605" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>1</v>
+      </c>
+      <c r="R605" t="n">
+        <v>5</v>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>1840672869</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1840672869</t>
+        </is>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>빌리캣바버샵 성수본점</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr"/>
+      <c r="D606" t="inlineStr"/>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>0507-1442-9998</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 동일로 31</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://billycatbarbershopseoul.vercel.app/ko</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr"/>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P606" t="n">
+        <v>1512</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>419</v>
+      </c>
+      <c r="R606" t="n">
+        <v>1931</v>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>38654562</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38654562</t>
+        </is>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>넘버인테리어</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>kare-korea@naver.com</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>0507-1413-4356</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 매봉길 15</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr"/>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P607" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>0</v>
+      </c>
+      <c r="R607" t="n">
+        <v>0</v>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>1446473953</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446473953</t>
+        </is>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>감성인테리어</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>damda001@naver.com</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>0507-1328-4321</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로2길 30</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr"/>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P608" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>0</v>
+      </c>
+      <c r="R608" t="n">
+        <v>0</v>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>1198525354</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198525354</t>
+        </is>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>다준디자인</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>khb960@naver.com</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>0507-1429-5607</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로15가길 23</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/khb960</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr"/>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P609" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>0</v>
+      </c>
+      <c r="R609" t="n">
+        <v>0</v>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
         <is>
           <t>1639257377</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="U609" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1639257377</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr">
+      <c r="V609" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
